--- a/results/regression_output/full_sample_covid_analysis/price_robustness_matrix.xlsx
+++ b/results/regression_output/full_sample_covid_analysis/price_robustness_matrix.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,132 +417,132 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>spec_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>control_spec</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>price_measure</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>price_description</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>controls</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>n_controls</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>eu_pre_elasticity</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>eu_pre_se</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>eu_pre_pval</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>eap_pre_elasticity</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>eap_pre_se</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>eap_pre_pval</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>eu_covid_elasticity</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>eu_covid_se</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>eu_covid_pval</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>eap_covid_elasticity</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>eap_covid_se</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>eap_covid_pval</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>ratio_pre</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>ratio_covid</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>price_x_covid_coef</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>price_x_covid_pval</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>triple_interaction_coef</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>triple_interaction_pval</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>n_obs</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>r_squared</t>
         </is>
@@ -588,64 +576,64 @@
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2307512919712725</v>
+        <v>-0.1908065607759881</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08011613882156479</v>
+        <v>0.07441262224129772</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004170894996242902</v>
+        <v>0.01067788454604046</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.3266158705639082</v>
+        <v>-0.3586832490258667</v>
       </c>
       <c r="K2" t="n">
-        <v>0.156003841127597</v>
+        <v>0.1258002088862993</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03687180626359043</v>
+        <v>0.004563045486056572</v>
       </c>
       <c r="M2" t="n">
-        <v>0.07862122525909832</v>
+        <v>0.1086117580486053</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1352094510115218</v>
+        <v>0.1331184255773259</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5612206948740077</v>
+        <v>0.41500303022429</v>
       </c>
       <c r="P2" t="n">
-        <v>0.08809142046950814</v>
+        <v>0.06278039569190315</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1932180655105882</v>
+        <v>0.1706963681708208</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6486776291532497</v>
+        <v>0.713209218400954</v>
       </c>
       <c r="S2" t="n">
-        <v>1.415445468468148</v>
+        <v>1.879826603273721</v>
       </c>
       <c r="T2" t="n">
-        <v>1.120453416735755</v>
+        <v>0.5780257756605695</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3093725172303708</v>
+        <v>0.2994183188245934</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0047171955487606</v>
+        <v>0.006939817270934512</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1053347738030455</v>
+        <v>0.1220453258931764</v>
       </c>
       <c r="X2" t="n">
-        <v>0.001870179957691676</v>
+        <v>0.0003131895913697225</v>
       </c>
       <c r="Y2" t="n">
         <v>495</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.4041421902151686</v>
+        <v>0.4222868362410958</v>
       </c>
     </row>
     <row r="3">
@@ -676,64 +664,64 @@
         <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1778789626958262</v>
+        <v>-0.1364606944014695</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05233559721715721</v>
+        <v>0.04739380292023907</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000738560271393629</v>
+        <v>0.004180523858242857</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.3128960633755908</v>
+        <v>-0.3329291586321067</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1402572362271211</v>
+        <v>0.1114265192535013</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02619399776906817</v>
+        <v>0.00296671404494453</v>
       </c>
       <c r="M3" t="n">
-        <v>0.06940315160896818</v>
+        <v>0.0971936324649034</v>
       </c>
       <c r="N3" t="n">
-        <v>0.08631144288523351</v>
+        <v>0.08260285374182259</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4217736271384878</v>
+        <v>0.2399777433067629</v>
       </c>
       <c r="P3" t="n">
-        <v>0.04365296888240751</v>
+        <v>0.0245511174660307</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1616758604107195</v>
+        <v>0.1370112169452358</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7872848152155436</v>
+        <v>0.8578707430841943</v>
       </c>
       <c r="S3" t="n">
-        <v>1.759039172668464</v>
+        <v>2.439743987031342</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6289767520696673</v>
+        <v>0.2526000607590842</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2472821143047944</v>
+        <v>0.2336543268663729</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0003506917450768476</v>
+        <v>0.0006067054574601105</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1092669179532039</v>
+        <v>0.1238259492317645</v>
       </c>
       <c r="X3" t="n">
-        <v>0.009437829329074887</v>
+        <v>0.003503187307031919</v>
       </c>
       <c r="Y3" t="n">
         <v>495</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.3742950513602701</v>
+        <v>0.3824041367382668</v>
       </c>
     </row>
     <row r="4">
@@ -764,64 +752,64 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2007181896571462</v>
+        <v>-0.1432353433987587</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06111605860064765</v>
+        <v>0.05177726682620148</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001104156518723087</v>
+        <v>0.005906518196401533</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.3298953016098962</v>
+        <v>-0.3504785606556576</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1442797199706152</v>
+        <v>0.1187486325964152</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02269835986900626</v>
+        <v>0.003331718724750354</v>
       </c>
       <c r="M4" t="n">
-        <v>0.06724403932764389</v>
+        <v>0.09937366898180935</v>
       </c>
       <c r="N4" t="n">
-        <v>0.09929078262762714</v>
+        <v>0.08999448954050022</v>
       </c>
       <c r="O4" t="n">
-        <v>0.49860656678851</v>
+        <v>0.2701000616232445</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0325752091482132</v>
+        <v>0.0108812817654662</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1678677134817271</v>
+        <v>0.1451629858822026</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8462238491533975</v>
+        <v>0.9402812715280882</v>
       </c>
       <c r="S4" t="n">
-        <v>1.643574516955349</v>
+        <v>2.446872066204681</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4844326645740569</v>
+        <v>0.1094986416115727</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2679622289847901</v>
+        <v>0.242609012380568</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0006739709029492946</v>
+        <v>0.001060065235822805</v>
       </c>
       <c r="W4" t="n">
-        <v>0.09450828177331931</v>
+        <v>0.1187508300405558</v>
       </c>
       <c r="X4" t="n">
-        <v>0.007538441403443841</v>
+        <v>0.002731992115759363</v>
       </c>
       <c r="Y4" t="n">
         <v>495</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.3664480282689816</v>
+        <v>0.379178849657785</v>
       </c>
     </row>
     <row r="5">
@@ -852,64 +840,64 @@
         <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1609222316540224</v>
+        <v>-0.1593801905328969</v>
       </c>
       <c r="H5" t="n">
-        <v>0.040077131161853</v>
+        <v>0.0393384671571191</v>
       </c>
       <c r="I5" t="n">
-        <v>6.974339522525241e-05</v>
+        <v>6.011233734004584e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3536767928435008</v>
+        <v>-0.3538577295275603</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1391536375299035</v>
+        <v>0.1381615423428651</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01137429962403114</v>
+        <v>0.01076240081793411</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1550562526889133</v>
+        <v>0.155313073613081</v>
       </c>
       <c r="N5" t="n">
-        <v>0.09924888479046998</v>
+        <v>0.0982622259608591</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1189336645852421</v>
+        <v>0.1146853001705139</v>
       </c>
       <c r="P5" t="n">
-        <v>0.04427350880197854</v>
+        <v>0.04370246834340927</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1707591613651468</v>
+        <v>0.1695623367957826</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7955441066996558</v>
+        <v>0.7967299313572329</v>
       </c>
       <c r="S5" t="n">
-        <v>2.197811882225786</v>
+        <v>2.220211485156446</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2855319152514521</v>
+        <v>0.2813830627824784</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3159784843429357</v>
+        <v>0.3146932641459779</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0005511121638330785</v>
+        <v>0.0005221477718919676</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0819718173025437</v>
+        <v>0.08286693372499168</v>
       </c>
       <c r="X5" t="n">
-        <v>0.03795807753536984</v>
+        <v>0.03615780316456352</v>
       </c>
       <c r="Y5" t="n">
         <v>495</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.3380982422906013</v>
+        <v>0.3384057745921305</v>
       </c>
     </row>
     <row r="6">
@@ -940,64 +928,64 @@
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.158681731329181</v>
+        <v>-0.1569434116500701</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05145175100825338</v>
+        <v>0.05039527186887836</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002170053355405432</v>
+        <v>0.001964314947974444</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3415664048831428</v>
+        <v>-0.3417128272472357</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1551498640578301</v>
+        <v>0.1539856791575077</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0282160471672781</v>
+        <v>0.02698671061535518</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1573035177687853</v>
+        <v>0.1576019215748242</v>
       </c>
       <c r="N6" t="n">
-        <v>0.103941509890437</v>
+        <v>0.1026977164102668</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1308982147924229</v>
+        <v>0.1255943976835276</v>
       </c>
       <c r="P6" t="n">
-        <v>0.05500494209334292</v>
+        <v>0.05443345894513896</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1826023764570556</v>
+        <v>0.1811982683528159</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7633826454143984</v>
+        <v>0.7640073163452419</v>
       </c>
       <c r="S6" t="n">
-        <v>2.15252507029037</v>
+        <v>2.177299598973533</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3496739480053631</v>
+        <v>0.3453857567294681</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3159852490979662</v>
+        <v>0.3145453332248944</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0005149282713838854</v>
+        <v>0.0004849649108555898</v>
       </c>
       <c r="W6" t="n">
-        <v>0.08058609787851953</v>
+        <v>0.08160095296748032</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01624096613805581</v>
+        <v>0.01488536988520317</v>
       </c>
       <c r="Y6" t="n">
         <v>495</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.3377850176261024</v>
+        <v>0.3381409205256601</v>
       </c>
     </row>
     <row r="7">
@@ -1028,64 +1016,64 @@
         <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2175788649683579</v>
+        <v>-0.1553543154909819</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0786557787878671</v>
+        <v>0.06303021255458133</v>
       </c>
       <c r="I7" t="n">
-        <v>0.005909900075440788</v>
+        <v>0.01409154624590658</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3819327537076589</v>
+        <v>-0.4183164000911773</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1519407082073732</v>
+        <v>0.1187380505751605</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01230342646580196</v>
+        <v>0.0004712910068762621</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1402998069794595</v>
+        <v>0.1762019955230177</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1445023363833731</v>
+        <v>0.1321795283334539</v>
       </c>
       <c r="O7" t="n">
-        <v>0.332122920556936</v>
+        <v>0.1832050097293021</v>
       </c>
       <c r="P7" t="n">
-        <v>0.04848656608958578</v>
+        <v>0.01785109638434906</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1961447334036046</v>
+        <v>0.1692039517198653</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8048703717354584</v>
+        <v>0.9160267753934808</v>
       </c>
       <c r="S7" t="n">
-        <v>1.755376165617937</v>
+        <v>2.692660315029741</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3455925359661003</v>
+        <v>0.1013104098586507</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3578786719478174</v>
+        <v>0.3315563110139996</v>
       </c>
       <c r="V7" t="n">
-        <v>0.003322766454101123</v>
+        <v>0.004524901393742731</v>
       </c>
       <c r="W7" t="n">
-        <v>0.07254064784942731</v>
+        <v>0.1046111854615267</v>
       </c>
       <c r="X7" t="n">
-        <v>0.006086718945727876</v>
+        <v>0.001219748587644842</v>
       </c>
       <c r="Y7" t="n">
         <v>495</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.35443899116738</v>
+        <v>0.3768682934293673</v>
       </c>
     </row>
     <row r="8">
@@ -1116,64 +1104,64 @@
         <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1858391861270978</v>
+        <v>-0.1852893604476891</v>
       </c>
       <c r="H8" t="n">
-        <v>0.05156981770914006</v>
+        <v>0.05092202277400479</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0003495518248060048</v>
+        <v>0.000306467766669094</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.348799118411156</v>
+        <v>-0.3506577463163462</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1439827808363816</v>
+        <v>0.142932098770189</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01581586422467063</v>
+        <v>0.01454059203119495</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1455786038060637</v>
+        <v>0.1442811853744973</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1110939482070448</v>
+        <v>0.1094396141579807</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1907392939442316</v>
+        <v>0.1880663167692185</v>
       </c>
       <c r="P8" t="n">
-        <v>0.05396963746291444</v>
+        <v>0.05126825892725741</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1776839339099296</v>
+        <v>0.1760570296726802</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7614695793332582</v>
+        <v>0.7710333112954051</v>
       </c>
       <c r="S8" t="n">
-        <v>1.876886816393006</v>
+        <v>1.892487218203465</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3707250657164669</v>
+        <v>0.3553357202755517</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3314177899331615</v>
+        <v>0.3295705458221864</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0008233132299599877</v>
+        <v>0.0007295185794191639</v>
       </c>
       <c r="W8" t="n">
-        <v>0.07135096594090889</v>
+        <v>0.0723554594214172</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03659488849532555</v>
+        <v>0.03593466542724699</v>
       </c>
       <c r="Y8" t="n">
         <v>495</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.3434810995239769</v>
+        <v>0.3449049784719663</v>
       </c>
     </row>
     <row r="9">
@@ -1204,64 +1192,64 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1691523696373219</v>
+        <v>-0.1676242653923001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04679308956512318</v>
+        <v>0.0459573950991576</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0003349653354229876</v>
+        <v>0.0002964299160332917</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3496245898519463</v>
+        <v>-0.3498175481283099</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1481990570104949</v>
+        <v>0.1471080883824976</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01874971572460504</v>
+        <v>0.01783189491473158</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1538514679127076</v>
+        <v>0.1540962292337341</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1059702462373275</v>
+        <v>0.1049409266491931</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1472549035315285</v>
+        <v>0.142702765369304</v>
       </c>
       <c r="P9" t="n">
-        <v>0.04863186698086261</v>
+        <v>0.04806953732053527</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1790738836366883</v>
+        <v>0.1777773313817092</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7860758621862087</v>
+        <v>0.7869847517457584</v>
       </c>
       <c r="S9" t="n">
-        <v>2.066921028665299</v>
+        <v>2.086914727468681</v>
       </c>
       <c r="T9" t="n">
-        <v>0.316096216959434</v>
+        <v>0.3119449292144788</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3230038375500295</v>
+        <v>0.3217204946260342</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0007422431891261905</v>
+        <v>0.0007087869372151001</v>
       </c>
       <c r="W9" t="n">
-        <v>0.07525261928277946</v>
+        <v>0.07616659082281098</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02153837448492868</v>
+        <v>0.01995679607922374</v>
       </c>
       <c r="Y9" t="n">
         <v>495</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.3362008196271574</v>
+        <v>0.3365123578311333</v>
       </c>
     </row>
     <row r="10">
@@ -1292,64 +1280,64 @@
         <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1326298141189974</v>
+        <v>-0.1262055597773079</v>
       </c>
       <c r="H10" t="n">
-        <v>0.06302022998593464</v>
+        <v>0.05948594775533134</v>
       </c>
       <c r="I10" t="n">
-        <v>0.03590413183656449</v>
+        <v>0.03443719106011733</v>
       </c>
       <c r="J10" t="n">
-        <v>0.04131468566669574</v>
+        <v>0.01325931823177962</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1213956525007208</v>
+        <v>0.1031664911324486</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7337720511297292</v>
+        <v>0.8977942396305112</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.03090342291416624</v>
+        <v>-0.01032312465879573</v>
       </c>
       <c r="N10" t="n">
-        <v>0.08775398640148849</v>
+        <v>0.08261530236271691</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7248893885072798</v>
+        <v>0.9006177074274304</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2241585747814311</v>
+        <v>0.2191554354725503</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.139843673942637</v>
+        <v>0.1224736626770367</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1096792592881815</v>
+        <v>0.07424617312978121</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3115037590991993</v>
+        <v>0.1050612845834679</v>
       </c>
       <c r="T10" t="n">
-        <v>7.25351930768407</v>
+        <v>21.22956398534051</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1017263912048311</v>
+        <v>0.1158824351185122</v>
       </c>
       <c r="V10" t="n">
-        <v>0.09647315101634102</v>
+        <v>0.0438590962528842</v>
       </c>
       <c r="W10" t="n">
-        <v>0.08111749790990426</v>
+        <v>0.09001368212225851</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01440755641986868</v>
+        <v>0.006169527414706444</v>
       </c>
       <c r="Y10" t="n">
         <v>495</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.3273437851333963</v>
+        <v>0.338712995102226</v>
       </c>
     </row>
     <row r="11">
@@ -1380,64 +1368,64 @@
         <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.136189931053204</v>
+        <v>-0.1297896329218179</v>
       </c>
       <c r="H11" t="n">
-        <v>0.06234026374382214</v>
+        <v>0.05923820461828493</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02944475361984034</v>
+        <v>0.02897831532357076</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.002827061645768902</v>
+        <v>-0.02690173803271029</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1044161300083381</v>
+        <v>0.09013509971849361</v>
       </c>
       <c r="L11" t="n">
-        <v>0.9784122565225353</v>
+        <v>0.7654931805333591</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.01591052133490234</v>
+        <v>0.004373922794425056</v>
       </c>
       <c r="N11" t="n">
-        <v>0.09059708718338465</v>
+        <v>0.08580179042821556</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8606746708027566</v>
+        <v>0.9593669884911344</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1991036426394365</v>
+        <v>0.1961867092588476</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1272916556211172</v>
+        <v>0.1137628302368161</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1185021475480077</v>
+        <v>0.08531722025896693</v>
       </c>
       <c r="S11" t="n">
-        <v>0.02075822804157586</v>
+        <v>0.2072718554409908</v>
       </c>
       <c r="T11" t="n">
-        <v>12.51396094750648</v>
+        <v>44.85372021401579</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1202794097183017</v>
+        <v>0.1341635557162429</v>
       </c>
       <c r="V11" t="n">
-        <v>0.06797726974125573</v>
+        <v>0.03119967855220906</v>
       </c>
       <c r="W11" t="n">
-        <v>0.08165129456690373</v>
+        <v>0.08892489157531495</v>
       </c>
       <c r="X11" t="n">
-        <v>0.009371764719734887</v>
+        <v>0.004400195069725665</v>
       </c>
       <c r="Y11" t="n">
         <v>495</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.3085019678001172</v>
+        <v>0.3151825228869206</v>
       </c>
     </row>
     <row r="12">
@@ -1468,64 +1456,64 @@
         <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1458271344408896</v>
+        <v>-0.1347213984071494</v>
       </c>
       <c r="H12" t="n">
-        <v>0.06529740472246064</v>
+        <v>0.05986491470990148</v>
       </c>
       <c r="I12" t="n">
-        <v>0.02603165362864379</v>
+        <v>0.02491411983624525</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.01875178640985856</v>
+        <v>-0.04929591654731119</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1023669801927117</v>
+        <v>0.08849858097863554</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8547394177948937</v>
+        <v>0.5777929716238019</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.03443654571919372</v>
+        <v>-0.004339375074473406</v>
       </c>
       <c r="N12" t="n">
-        <v>0.08793298635901592</v>
+        <v>0.08156096999198173</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6955262405464011</v>
+        <v>0.9575934096785721</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1734368882524471</v>
+        <v>0.1727825374767906</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1222386334974716</v>
+        <v>0.1093528399551743</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1566524302604904</v>
+        <v>0.1148132353638542</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1285891441380514</v>
+        <v>0.3659100716749622</v>
       </c>
       <c r="T12" t="n">
-        <v>5.036419438427573</v>
+        <v>39.81737796605614</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1113905887216959</v>
+        <v>0.130382023332676</v>
       </c>
       <c r="V12" t="n">
-        <v>0.05922784315634178</v>
+        <v>0.01902234570686523</v>
       </c>
       <c r="W12" t="n">
-        <v>0.08079808594060975</v>
+        <v>0.09169643069142575</v>
       </c>
       <c r="X12" t="n">
-        <v>0.01074768159354744</v>
+        <v>0.005025832830633847</v>
       </c>
       <c r="Y12" t="n">
         <v>495</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.2889189724666913</v>
+        <v>0.3006611222339646</v>
       </c>
     </row>
     <row r="13">
@@ -1556,64 +1544,64 @@
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1236952235138722</v>
+        <v>-0.1237787189543719</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0525699965188996</v>
+        <v>0.05258208320891804</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01906187272318416</v>
+        <v>0.01900894609287973</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.006355234986581734</v>
+        <v>-0.005893311295613213</v>
       </c>
       <c r="K13" t="n">
-        <v>0.08487294564251917</v>
+        <v>0.08493846454147885</v>
       </c>
       <c r="L13" t="n">
-        <v>0.9403445465623825</v>
+        <v>0.9447158967789728</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.002611282631998141</v>
+        <v>-0.002937585010328717</v>
       </c>
       <c r="N13" t="n">
-        <v>0.07900085470001121</v>
+        <v>0.07896591941327742</v>
       </c>
       <c r="O13" t="n">
-        <v>0.973646563506648</v>
+        <v>0.9703418006067994</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2004141997056586</v>
+        <v>0.2008770177785392</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.1091620621096018</v>
+        <v>0.1091958704520013</v>
       </c>
       <c r="R13" t="n">
-        <v>0.06703915736730481</v>
+        <v>0.0664970263123521</v>
       </c>
       <c r="S13" t="n">
-        <v>0.05137817618211432</v>
+        <v>0.04761166818817734</v>
       </c>
       <c r="T13" t="n">
-        <v>76.74933277992302</v>
+        <v>68.3816866821706</v>
       </c>
       <c r="U13" t="n">
-        <v>0.121083940881874</v>
+        <v>0.1208411339440432</v>
       </c>
       <c r="V13" t="n">
-        <v>0.04063205955955462</v>
+        <v>0.04083837525622336</v>
       </c>
       <c r="W13" t="n">
-        <v>0.08568549381036628</v>
+        <v>0.0859291951301092</v>
       </c>
       <c r="X13" t="n">
-        <v>0.01516918285942426</v>
+        <v>0.01500748795024864</v>
       </c>
       <c r="Y13" t="n">
         <v>495</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.2347443086599851</v>
+        <v>0.2350710624732134</v>
       </c>
     </row>
     <row r="14">
@@ -1644,64 +1632,64 @@
         <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1179897588082664</v>
+        <v>-0.1180517508691258</v>
       </c>
       <c r="H14" t="n">
-        <v>0.05001822322576178</v>
+        <v>0.05004448649895173</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01876265848120928</v>
+        <v>0.01876261988898009</v>
       </c>
       <c r="J14" t="n">
-        <v>0.004640789516313734</v>
+        <v>0.005018566042800515</v>
       </c>
       <c r="K14" t="n">
-        <v>0.08727922990137911</v>
+        <v>0.08740571315205253</v>
       </c>
       <c r="L14" t="n">
-        <v>0.9576191403430312</v>
+        <v>0.95423909813853</v>
       </c>
       <c r="M14" t="n">
-        <v>0.01244459261886875</v>
+        <v>0.01224683582631203</v>
       </c>
       <c r="N14" t="n">
-        <v>0.08347957343539122</v>
+        <v>0.08348352438797091</v>
       </c>
       <c r="O14" t="n">
-        <v>0.881563777499325</v>
+        <v>0.8834377199505665</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2203260106542204</v>
+        <v>0.2208294892241674</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.115275561071151</v>
+        <v>0.1153684564797534</v>
       </c>
       <c r="R14" t="n">
-        <v>0.05661416339516245</v>
+        <v>0.05625126398205471</v>
       </c>
       <c r="S14" t="n">
-        <v>0.03933213834138798</v>
+        <v>0.04251157654039526</v>
       </c>
       <c r="T14" t="n">
-        <v>17.70455790735628</v>
+        <v>18.03155462815306</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1304343514271351</v>
+        <v>0.1302985866954379</v>
       </c>
       <c r="V14" t="n">
-        <v>0.05162243610422768</v>
+        <v>0.05181368288597943</v>
       </c>
       <c r="W14" t="n">
-        <v>0.08525086971077149</v>
+        <v>0.08551233648592904</v>
       </c>
       <c r="X14" t="n">
-        <v>0.01438969476045715</v>
+        <v>0.01414634732032871</v>
       </c>
       <c r="Y14" t="n">
         <v>495</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.2437790793768353</v>
+        <v>0.2442144654768807</v>
       </c>
     </row>
     <row r="15">
@@ -1732,64 +1720,64 @@
         <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1246928228106956</v>
+        <v>-0.1133965606768705</v>
       </c>
       <c r="H15" t="n">
-        <v>0.05816200931848093</v>
+        <v>0.05116464833415591</v>
       </c>
       <c r="I15" t="n">
-        <v>0.03258929529851273</v>
+        <v>0.02718130542144759</v>
       </c>
       <c r="J15" t="n">
-        <v>0.01987868780118908</v>
+        <v>-0.01789116889871011</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1032979908888626</v>
+        <v>0.08549286737388682</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8474861788686616</v>
+        <v>0.8343336240342616</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.01148571729985833</v>
+        <v>0.01761429226320586</v>
       </c>
       <c r="N15" t="n">
-        <v>0.08186068815494027</v>
+        <v>0.07297182576773384</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8884807739711096</v>
+        <v>0.8093693115093483</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2164579719119042</v>
+        <v>0.2098153262066337</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1233031409928314</v>
+        <v>0.1062895425475514</v>
       </c>
       <c r="R15" t="n">
-        <v>0.07987061510604421</v>
+        <v>0.04900706124524468</v>
       </c>
       <c r="S15" t="n">
-        <v>0.159421267023269</v>
+        <v>0.1577752340275287</v>
       </c>
       <c r="T15" t="n">
-        <v>18.8458383800352</v>
+        <v>11.91165237134805</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1132071055108373</v>
+        <v>0.1310108529400764</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0500167827459288</v>
+        <v>0.01215583741001525</v>
       </c>
       <c r="W15" t="n">
-        <v>0.08337217859987783</v>
+        <v>0.09669564216526749</v>
       </c>
       <c r="X15" t="n">
-        <v>0.01717542549390139</v>
+        <v>0.00717407707458273</v>
       </c>
       <c r="Y15" t="n">
         <v>495</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.2412779042540585</v>
+        <v>0.2536644278165219</v>
       </c>
     </row>
     <row r="16">
@@ -1820,64 +1808,64 @@
         <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1248505429380214</v>
+        <v>-0.1252838977856711</v>
       </c>
       <c r="H16" t="n">
-        <v>0.05299727075687981</v>
+        <v>0.053149844814891</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01892013117813951</v>
+        <v>0.01885031563166062</v>
       </c>
       <c r="J16" t="n">
-        <v>0.006366185349905198</v>
+        <v>0.006841298475382257</v>
       </c>
       <c r="K16" t="n">
-        <v>0.08426572649105414</v>
+        <v>0.08455664794244065</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9398122286616146</v>
+        <v>0.9355519238850687</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.005480360576955209</v>
+        <v>-0.006341097771190879</v>
       </c>
       <c r="N16" t="n">
-        <v>0.08031120662649389</v>
+        <v>0.08046583670173586</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9456262690594153</v>
+        <v>0.9372235950727648</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2081083214487716</v>
+        <v>0.2083804599905848</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.108886399545113</v>
+        <v>0.1091818717004458</v>
       </c>
       <c r="R16" t="n">
-        <v>0.05662137249285948</v>
+        <v>0.05696744252827446</v>
       </c>
       <c r="S16" t="n">
-        <v>0.05099044986184413</v>
+        <v>0.05460636679013595</v>
       </c>
       <c r="T16" t="n">
-        <v>37.97347246162275</v>
+        <v>32.8618904028427</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1193701823610662</v>
+        <v>0.1189428000144802</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04852568785187383</v>
+        <v>0.04960217034247538</v>
       </c>
       <c r="W16" t="n">
-        <v>0.08237195373780018</v>
+        <v>0.08259636150072233</v>
       </c>
       <c r="X16" t="n">
-        <v>0.01398253819762707</v>
+        <v>0.01400686281386121</v>
       </c>
       <c r="Y16" t="n">
         <v>495</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.239203888634389</v>
+        <v>0.2400270433502746</v>
       </c>
     </row>
     <row r="17">
@@ -1908,64 +1896,64 @@
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.124807839122179</v>
+        <v>-0.1248810907624443</v>
       </c>
       <c r="H17" t="n">
-        <v>0.05211490435753704</v>
+        <v>0.05213384055739632</v>
       </c>
       <c r="I17" t="n">
-        <v>0.01704127180721038</v>
+        <v>0.01701674044972168</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.005054611283901722</v>
+        <v>-0.004587870131853924</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0862569003034529</v>
+        <v>0.08634306907404116</v>
       </c>
       <c r="L17" t="n">
-        <v>0.9532975319285817</v>
+        <v>0.9576480097092415</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.003673031389668402</v>
+        <v>-0.003998859353855813</v>
       </c>
       <c r="N17" t="n">
-        <v>0.07863417887777575</v>
+        <v>0.07860247978150307</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9627651167141</v>
+        <v>0.9594484811325019</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2006787547497864</v>
+        <v>0.2011443941575537</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.1100063446085739</v>
+        <v>0.110051512784309</v>
       </c>
       <c r="R17" t="n">
-        <v>0.06878819714959894</v>
+        <v>0.06826262145077289</v>
       </c>
       <c r="S17" t="n">
-        <v>0.04049914908753107</v>
+        <v>0.03673790886869514</v>
       </c>
       <c r="T17" t="n">
-        <v>54.63573094263796</v>
+        <v>50.3004422907759</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1211348077325106</v>
+        <v>0.1208822314085885</v>
       </c>
       <c r="V17" t="n">
-        <v>0.04025537160643</v>
+        <v>0.04047096313315524</v>
       </c>
       <c r="W17" t="n">
-        <v>0.08459855830117746</v>
+        <v>0.08485003288081916</v>
       </c>
       <c r="X17" t="n">
-        <v>0.01473151779857185</v>
+        <v>0.01452318463814284</v>
       </c>
       <c r="Y17" t="n">
         <v>495</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.2341465476733375</v>
+        <v>0.2344793471696709</v>
       </c>
     </row>
     <row r="18">
@@ -1996,64 +1984,64 @@
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1138698802857682</v>
+        <v>-0.1004736609465064</v>
       </c>
       <c r="H18" t="n">
-        <v>0.03707638272253848</v>
+        <v>0.03188936237970107</v>
       </c>
       <c r="I18" t="n">
-        <v>0.002265851925066897</v>
+        <v>0.001741541322282325</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1424442720793432</v>
+        <v>-0.1641684174738484</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1158284937336795</v>
+        <v>0.0945446491607419</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2194434480945362</v>
+        <v>0.08320070799597001</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.05839300509334948</v>
+        <v>-0.03377957919252025</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0437676326802636</v>
+        <v>0.03869652304656652</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1828511966596127</v>
+        <v>0.3831807977694486</v>
       </c>
       <c r="P18" t="n">
-        <v>0.05064036242871599</v>
+        <v>0.05707942162693071</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.1272601631941229</v>
+        <v>0.1075090585158286</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6908790361395991</v>
+        <v>0.5957412100207171</v>
       </c>
       <c r="S18" t="n">
-        <v>1.250938981597807</v>
+        <v>1.633944816256412</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8672333672117097</v>
+        <v>1.68976118090807</v>
       </c>
       <c r="U18" t="n">
-        <v>0.05547687519241877</v>
+        <v>0.0666940817539861</v>
       </c>
       <c r="V18" t="n">
-        <v>0.01749562933237159</v>
+        <v>0.002487783151898793</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1376077593156404</v>
+        <v>0.154553757346793</v>
       </c>
       <c r="X18" t="n">
-        <v>0.003814303314638057</v>
+        <v>0.000904608894577219</v>
       </c>
       <c r="Y18" t="n">
         <v>495</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.3324292401939322</v>
+        <v>0.3496407568283366</v>
       </c>
     </row>
     <row r="19">
@@ -2084,64 +2072,64 @@
         <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.112814097265853</v>
+        <v>-0.09882616851591158</v>
       </c>
       <c r="H19" t="n">
-        <v>0.03569345949327511</v>
+        <v>0.03024853796771937</v>
       </c>
       <c r="I19" t="n">
-        <v>0.00168320443487735</v>
+        <v>0.001171659664372493</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1700543724292658</v>
+        <v>-0.1916220243525119</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1067119604108437</v>
+        <v>0.08605113305655729</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1117491469861132</v>
+        <v>0.0264645680275668</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.04348957336421171</v>
+        <v>-0.01656351923638708</v>
       </c>
       <c r="N19" t="n">
-        <v>0.04716865677351038</v>
+        <v>0.04162170040601392</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3570342027050961</v>
+        <v>0.6908575939252999</v>
       </c>
       <c r="P19" t="n">
-        <v>0.03933666370670921</v>
+        <v>0.04707035502939569</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.1204597406934358</v>
+        <v>0.10145161271346</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7441605313312192</v>
+        <v>0.6429002728063056</v>
       </c>
       <c r="S19" t="n">
-        <v>1.507385836971445</v>
+        <v>1.938980608376613</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9045079237102843</v>
+        <v>2.841808818381457</v>
       </c>
       <c r="U19" t="n">
-        <v>0.06932452390164129</v>
+        <v>0.08226264927952451</v>
       </c>
       <c r="V19" t="n">
-        <v>0.02506092073063027</v>
+        <v>0.004206328280499605</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1400665122343337</v>
+        <v>0.1564297301023831</v>
       </c>
       <c r="X19" t="n">
-        <v>0.002805731400640665</v>
+        <v>0.0006418748885739234</v>
       </c>
       <c r="Y19" t="n">
         <v>495</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.3212513813724847</v>
+        <v>0.333733725899572</v>
       </c>
     </row>
     <row r="20">
@@ -2172,64 +2160,64 @@
         <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1217273751041833</v>
+        <v>-0.1016287865196637</v>
       </c>
       <c r="H20" t="n">
-        <v>0.04135170680752829</v>
+        <v>0.03192972794310017</v>
       </c>
       <c r="I20" t="n">
-        <v>0.003414327627214053</v>
+        <v>0.001561290413683469</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1868818385839032</v>
+        <v>-0.2129134325110132</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1098915151668757</v>
+        <v>0.09127175985279461</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0897225561921593</v>
+        <v>0.02011067903613784</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.06129678216967495</v>
+        <v>-0.02340417174706023</v>
       </c>
       <c r="N20" t="n">
-        <v>0.04778875193050667</v>
+        <v>0.03956810630090955</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2002845183640507</v>
+        <v>0.554494670691613</v>
       </c>
       <c r="P20" t="n">
-        <v>0.007843497827575069</v>
+        <v>0.02200665710681832</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.120611627971346</v>
+        <v>0.1041941853568474</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9481787660682348</v>
+        <v>0.8328224459999687</v>
       </c>
       <c r="S20" t="n">
-        <v>1.535249063113009</v>
+        <v>2.095011067261121</v>
       </c>
       <c r="T20" t="n">
-        <v>0.127959373232082</v>
+        <v>0.9402877976052514</v>
       </c>
       <c r="U20" t="n">
-        <v>0.06043059293450832</v>
+        <v>0.07822461477260344</v>
       </c>
       <c r="V20" t="n">
-        <v>0.01199447195972891</v>
+        <v>0.0008859032695978097</v>
       </c>
       <c r="W20" t="n">
-        <v>0.13429474347697</v>
+        <v>0.1566954748452281</v>
       </c>
       <c r="X20" t="n">
-        <v>0.002176470548060694</v>
+        <v>0.0004735127307073927</v>
       </c>
       <c r="Y20" t="n">
         <v>495</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.3058510380166674</v>
+        <v>0.3247912492412734</v>
       </c>
     </row>
     <row r="21">
@@ -2260,64 +2248,64 @@
         <v>2</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.09787365838880295</v>
+        <v>-0.09831718580520386</v>
       </c>
       <c r="H21" t="n">
-        <v>0.02517602188895354</v>
+        <v>0.0252562924987465</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0001167887891151409</v>
+        <v>0.0001143918434927116</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.175396486137437</v>
+        <v>-0.1743801508006306</v>
       </c>
       <c r="K21" t="n">
-        <v>0.09722488184462742</v>
+        <v>0.09744282500950603</v>
       </c>
       <c r="L21" t="n">
-        <v>0.07190746271976134</v>
+        <v>0.07420855582883124</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.02892511105811954</v>
+        <v>-0.02924392372755673</v>
       </c>
       <c r="N21" t="n">
-        <v>0.03574566954042101</v>
+        <v>0.03586224386718907</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4188400651820787</v>
+        <v>0.4152530579993172</v>
       </c>
       <c r="P21" t="n">
-        <v>0.0398392033227835</v>
+        <v>0.04151513068744797</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.112358975230137</v>
+        <v>0.1126330060683895</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7230803154555134</v>
+        <v>0.7126116062366326</v>
       </c>
       <c r="S21" t="n">
-        <v>1.792070399991331</v>
+        <v>1.773648720439685</v>
       </c>
       <c r="T21" t="n">
-        <v>1.377322397923872</v>
+        <v>1.419615612262318</v>
       </c>
       <c r="U21" t="n">
-        <v>0.06894854733068341</v>
+        <v>0.06907326207764714</v>
       </c>
       <c r="V21" t="n">
-        <v>0.006843857618073601</v>
+        <v>0.006928244585759025</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1462871421295371</v>
+        <v>0.1468220194104314</v>
       </c>
       <c r="X21" t="n">
-        <v>0.00380239967292284</v>
+        <v>0.003777966062121996</v>
       </c>
       <c r="Y21" t="n">
         <v>495</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.2539413900480159</v>
+        <v>0.2543232147727231</v>
       </c>
     </row>
     <row r="22">
@@ -2348,64 +2336,64 @@
         <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.09395639913076315</v>
+        <v>-0.0943577203152131</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0234341324576754</v>
+        <v>0.0235875633016006</v>
       </c>
       <c r="I22" t="n">
-        <v>7.148020004565936e-05</v>
+        <v>7.417433766621073e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1624958028384285</v>
+        <v>-0.1614790012008076</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1026363626883031</v>
+        <v>0.1028991652887455</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1140884830258535</v>
+        <v>0.1172967422619837</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.01790999626745439</v>
+        <v>-0.01806578947358668</v>
       </c>
       <c r="N22" t="n">
-        <v>0.03966860930472589</v>
+        <v>0.03986827281565793</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6518580899497426</v>
+        <v>0.6506729611863624</v>
       </c>
       <c r="P22" t="n">
-        <v>0.06193400301614034</v>
+        <v>0.06378473149136982</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.1192799142971031</v>
+        <v>0.1195917433830061</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6038591262483584</v>
+        <v>0.5940572621155364</v>
       </c>
       <c r="S22" t="n">
-        <v>1.729480954376255</v>
+        <v>1.711349115486978</v>
       </c>
       <c r="T22" t="n">
-        <v>3.458069007456205</v>
+        <v>3.530691619351985</v>
       </c>
       <c r="U22" t="n">
-        <v>0.07604640286330876</v>
+        <v>0.07629193084162642</v>
       </c>
       <c r="V22" t="n">
-        <v>0.01793061959880271</v>
+        <v>0.01804350713366976</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1483834029912601</v>
+        <v>0.148971801850551</v>
       </c>
       <c r="X22" t="n">
-        <v>0.00427339540133409</v>
+        <v>0.004207075034887708</v>
       </c>
       <c r="Y22" t="n">
         <v>495</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.2592786587863564</v>
+        <v>0.2598293416297719</v>
       </c>
     </row>
     <row r="23">
@@ -2436,64 +2424,64 @@
         <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1065107637016878</v>
+        <v>-0.08501959467937518</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0346944366645074</v>
+        <v>0.02385452501836665</v>
       </c>
       <c r="I23" t="n">
-        <v>0.002273344512027986</v>
+        <v>0.00040507931538869</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1606225042959709</v>
+        <v>-0.1925059826812914</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1111525720003017</v>
+        <v>0.09015771029380448</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1491518889742824</v>
+        <v>0.03329525236678332</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.04291720933824947</v>
+        <v>-0.005864671243464667</v>
       </c>
       <c r="N23" t="n">
-        <v>0.04159752709585181</v>
+        <v>0.03221052971686993</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3027677175292252</v>
+        <v>0.8556092046209027</v>
       </c>
       <c r="P23" t="n">
-        <v>0.04489915500594653</v>
+        <v>0.05338367877332142</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.1232349773133212</v>
+        <v>0.1047855352793396</v>
       </c>
       <c r="R23" t="n">
-        <v>0.7157808349428083</v>
+        <v>0.6106876449304313</v>
       </c>
       <c r="S23" t="n">
-        <v>1.508040114573187</v>
+        <v>2.264254298168175</v>
       </c>
       <c r="T23" t="n">
-        <v>1.046180674332212</v>
+        <v>9.102586753317137</v>
       </c>
       <c r="U23" t="n">
-        <v>0.06359355436343835</v>
+        <v>0.07915492343591052</v>
       </c>
       <c r="V23" t="n">
-        <v>0.005823528063125583</v>
+        <v>0.0002859957142193892</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1419281049384791</v>
+        <v>0.1667347380187023</v>
       </c>
       <c r="X23" t="n">
-        <v>0.003284197993139948</v>
+        <v>0.0006957418650876956</v>
       </c>
       <c r="Y23" t="n">
         <v>495</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.2562506536198197</v>
+        <v>0.2783776763754089</v>
       </c>
     </row>
     <row r="24">
@@ -2524,64 +2512,64 @@
         <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1019288271420668</v>
+        <v>-0.1024904349959379</v>
       </c>
       <c r="H24" t="n">
-        <v>0.02766134748908417</v>
+        <v>0.0278996486601185</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0002572674147527376</v>
+        <v>0.0002686100581728024</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.166749400145179</v>
+        <v>-0.1669002789839438</v>
       </c>
       <c r="K24" t="n">
-        <v>0.09578037925905344</v>
+        <v>0.09591289885673115</v>
       </c>
       <c r="L24" t="n">
-        <v>0.08238874546690189</v>
+        <v>0.08253493398956468</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.03513778076782451</v>
+        <v>-0.03559012186479286</v>
       </c>
       <c r="N24" t="n">
-        <v>0.03767944907745851</v>
+        <v>0.03804302824873673</v>
       </c>
       <c r="O24" t="n">
-        <v>0.3515652208725981</v>
+        <v>0.3500309076714447</v>
       </c>
       <c r="P24" t="n">
-        <v>0.04102214792571258</v>
+        <v>0.04148209201771125</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1101411845190192</v>
+        <v>0.110412427849922</v>
       </c>
       <c r="R24" t="n">
-        <v>0.7097363247933086</v>
+        <v>0.7073196260039656</v>
       </c>
       <c r="S24" t="n">
-        <v>1.63593955528171</v>
+        <v>1.628447366728014</v>
       </c>
       <c r="T24" t="n">
-        <v>1.167465532236355</v>
+        <v>1.165550715878468</v>
       </c>
       <c r="U24" t="n">
-        <v>0.06679104637424228</v>
+        <v>0.06690031313114506</v>
       </c>
       <c r="V24" t="n">
-        <v>0.009347293349118102</v>
+        <v>0.01000797808195086</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1409805016966493</v>
+        <v>0.14148205787051</v>
       </c>
       <c r="X24" t="n">
-        <v>0.003476790478413427</v>
+        <v>0.003502737446950732</v>
       </c>
       <c r="Y24" t="n">
         <v>495</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.2555594302649364</v>
+        <v>0.2566272114239887</v>
       </c>
     </row>
     <row r="25">
@@ -2612,64 +2600,64 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.1009001110718021</v>
+        <v>-0.1013214926938874</v>
       </c>
       <c r="H25" t="n">
-        <v>0.02581111386111284</v>
+        <v>0.02591493190909908</v>
       </c>
       <c r="I25" t="n">
-        <v>0.000107109297770025</v>
+        <v>0.0001068526751519805</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.1698643653818366</v>
+        <v>-0.1688389564772287</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1020870795719678</v>
+        <v>0.1023281812440728</v>
       </c>
       <c r="L25" t="n">
-        <v>0.09683629736156174</v>
+        <v>0.09965682033661971</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.03299511140335887</v>
+        <v>-0.033299153512956</v>
       </c>
       <c r="N25" t="n">
-        <v>0.03588996895699989</v>
+        <v>0.03602259573994106</v>
       </c>
       <c r="O25" t="n">
-        <v>0.3584176657721743</v>
+        <v>0.3557832732970749</v>
       </c>
       <c r="P25" t="n">
-        <v>0.04133972366412585</v>
+        <v>0.04302945693132915</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.1158777551825301</v>
+        <v>0.1161637041057611</v>
       </c>
       <c r="R25" t="n">
-        <v>0.7214466727665221</v>
+        <v>0.7112459916471487</v>
       </c>
       <c r="S25" t="n">
-        <v>1.683490370599875</v>
+        <v>1.666368625137859</v>
       </c>
       <c r="T25" t="n">
-        <v>1.252904503299162</v>
+        <v>1.292208731810173</v>
       </c>
       <c r="U25" t="n">
-        <v>0.06790499966844322</v>
+        <v>0.0680223391809314</v>
       </c>
       <c r="V25" t="n">
-        <v>0.006724398320233194</v>
+        <v>0.00681274899722939</v>
       </c>
       <c r="W25" t="n">
-        <v>0.1432990893775193</v>
+        <v>0.1438460742276265</v>
       </c>
       <c r="X25" t="n">
-        <v>0.003510289432449909</v>
+        <v>0.00347424654252193</v>
       </c>
       <c r="Y25" t="n">
         <v>495</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.2519657990616854</v>
+        <v>0.2523589750532466</v>
       </c>
     </row>
   </sheetData>

--- a/results/regression_output/full_sample_covid_analysis/price_robustness_matrix.xlsx
+++ b/results/regression_output/full_sample_covid_analysis/price_robustness_matrix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z25"/>
+  <dimension ref="A1:AA25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,6 +547,11 @@
           <t>r_squared</t>
         </is>
       </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>df_resid</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -588,28 +593,28 @@
         <v>-0.3586832490258667</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1258002088862993</v>
+        <v>0.1114079656052606</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004563045486056572</v>
+        <v>0.001380347208086219</v>
       </c>
       <c r="M2" t="n">
         <v>0.1086117580486053</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1331184255773259</v>
+        <v>0.07195758655837421</v>
       </c>
       <c r="O2" t="n">
-        <v>0.41500303022429</v>
+        <v>0.1319278750416322</v>
       </c>
       <c r="P2" t="n">
         <v>0.06278039569190315</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1706963681708208</v>
+        <v>0.1179408932434768</v>
       </c>
       <c r="R2" t="n">
-        <v>0.713209218400954</v>
+        <v>0.5947879412813544</v>
       </c>
       <c r="S2" t="n">
         <v>1.879826603273721</v>
@@ -634,6 +639,9 @@
       </c>
       <c r="Z2" t="n">
         <v>0.4222868362410958</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>434</v>
       </c>
     </row>
     <row r="3">
@@ -676,28 +684,28 @@
         <v>-0.3329291586321067</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1114265192535013</v>
+        <v>0.1167778909793696</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00296671404494453</v>
+        <v>0.004564214508270714</v>
       </c>
       <c r="M3" t="n">
         <v>0.0971936324649034</v>
       </c>
       <c r="N3" t="n">
-        <v>0.08260285374182259</v>
+        <v>0.05573016781682696</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2399777433067629</v>
+        <v>0.08185834096701994</v>
       </c>
       <c r="P3" t="n">
         <v>0.0245511174660307</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1370112169452358</v>
+        <v>0.1214375057206401</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8578707430841943</v>
+        <v>0.839876855855858</v>
       </c>
       <c r="S3" t="n">
         <v>2.439743987031342</v>
@@ -722,6 +730,9 @@
       </c>
       <c r="Z3" t="n">
         <v>0.3824041367382668</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>439</v>
       </c>
     </row>
     <row r="4">
@@ -764,28 +775,28 @@
         <v>-0.3504785606556576</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1187486325964152</v>
+        <v>0.1298652008380899</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003331718724750354</v>
+        <v>0.007226513156255443</v>
       </c>
       <c r="M4" t="n">
         <v>0.09937366898180935</v>
       </c>
       <c r="N4" t="n">
-        <v>0.08999448954050022</v>
+        <v>0.05284827609630227</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2701000616232445</v>
+        <v>0.06071815597690922</v>
       </c>
       <c r="P4" t="n">
         <v>0.0108812817654662</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1451629858822026</v>
+        <v>0.1299954669441022</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9402812715280882</v>
+        <v>0.9333288953422176</v>
       </c>
       <c r="S4" t="n">
         <v>2.446872066204681</v>
@@ -810,6 +821,9 @@
       </c>
       <c r="Z4" t="n">
         <v>0.379178849657785</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>441</v>
       </c>
     </row>
     <row r="5">
@@ -852,28 +866,28 @@
         <v>-0.3538577295275603</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1381615423428651</v>
+        <v>0.1361065710659744</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01076240081793411</v>
+        <v>0.009638456911854165</v>
       </c>
       <c r="M5" t="n">
         <v>0.155313073613081</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0982622259608591</v>
+        <v>0.07820403868661886</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1146853001705139</v>
+        <v>0.04765082758897754</v>
       </c>
       <c r="P5" t="n">
         <v>0.04370246834340927</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1695623367957826</v>
+        <v>0.1353140122663301</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7967299313572329</v>
+        <v>0.7468701235207895</v>
       </c>
       <c r="S5" t="n">
         <v>2.220211485156446</v>
@@ -898,6 +912,9 @@
       </c>
       <c r="Z5" t="n">
         <v>0.3384057745921305</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>442</v>
       </c>
     </row>
     <row r="6">
@@ -940,28 +957,28 @@
         <v>-0.3417128272472357</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1539856791575077</v>
+        <v>0.1309100979924854</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02698671061535518</v>
+        <v>0.009354603047433407</v>
       </c>
       <c r="M6" t="n">
         <v>0.1576019215748242</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1026977164102668</v>
+        <v>0.08081523800364121</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1255943976835276</v>
+        <v>0.05179133588135487</v>
       </c>
       <c r="P6" t="n">
         <v>0.05443345894513896</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1811982683528159</v>
+        <v>0.1321989119521975</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7640073163452419</v>
+        <v>0.6807196342300188</v>
       </c>
       <c r="S6" t="n">
         <v>2.177299598973533</v>
@@ -986,6 +1003,9 @@
       </c>
       <c r="Z6" t="n">
         <v>0.3381409205256601</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>441</v>
       </c>
     </row>
     <row r="7">
@@ -1028,28 +1048,28 @@
         <v>-0.4183164000911773</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1187380505751605</v>
+        <v>0.1210348275559162</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0004712910068762621</v>
+        <v>0.0006011351914416707</v>
       </c>
       <c r="M7" t="n">
         <v>0.1762019955230177</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1321795283334539</v>
+        <v>0.07348566307227336</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1832050097293021</v>
+        <v>0.01691086741580072</v>
       </c>
       <c r="P7" t="n">
         <v>0.01785109638434906</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1692039517198653</v>
+        <v>0.1216546957945579</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9160267753934808</v>
+        <v>0.8834077847480817</v>
       </c>
       <c r="S7" t="n">
         <v>2.692660315029741</v>
@@ -1074,6 +1094,9 @@
       </c>
       <c r="Z7" t="n">
         <v>0.3768682934293673</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>440</v>
       </c>
     </row>
     <row r="8">
@@ -1116,28 +1139,28 @@
         <v>-0.3506577463163462</v>
       </c>
       <c r="K8" t="n">
-        <v>0.142932098770189</v>
+        <v>0.1342793207607255</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01454059203119495</v>
+        <v>0.009324514578489707</v>
       </c>
       <c r="M8" t="n">
         <v>0.1442811853744973</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1094396141579807</v>
+        <v>0.07370603774560643</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1880663167692185</v>
+        <v>0.0509164389700778</v>
       </c>
       <c r="P8" t="n">
         <v>0.05126825892725741</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1760570296726802</v>
+        <v>0.1278369863875255</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7710333112954051</v>
+        <v>0.6885819546299945</v>
       </c>
       <c r="S8" t="n">
         <v>1.892487218203465</v>
@@ -1162,6 +1185,9 @@
       </c>
       <c r="Z8" t="n">
         <v>0.3449049784719663</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -1204,28 +1230,28 @@
         <v>-0.3498175481283099</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1471080883824976</v>
+        <v>0.1373276326968269</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01783189491473158</v>
+        <v>0.01119232494960265</v>
       </c>
       <c r="M9" t="n">
         <v>0.1540962292337341</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1049409266491931</v>
+        <v>0.07629162331292183</v>
       </c>
       <c r="O9" t="n">
-        <v>0.142702765369304</v>
+        <v>0.04400236755850839</v>
       </c>
       <c r="P9" t="n">
         <v>0.04806953732053527</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1777773313817092</v>
+        <v>0.1373934621959423</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7869847517457584</v>
+        <v>0.7266042441438947</v>
       </c>
       <c r="S9" t="n">
         <v>2.086914727468681</v>
@@ -1250,6 +1276,9 @@
       </c>
       <c r="Z9" t="n">
         <v>0.3365123578311333</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>443</v>
       </c>
     </row>
     <row r="10">
@@ -1292,28 +1321,28 @@
         <v>0.01325931823177962</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1031664911324486</v>
+        <v>0.1172226599448566</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8977942396305112</v>
+        <v>0.9099938689621301</v>
       </c>
       <c r="M10" t="n">
         <v>-0.01032312465879573</v>
       </c>
       <c r="N10" t="n">
-        <v>0.08261530236271691</v>
+        <v>0.03420086826437137</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9006177074274304</v>
+        <v>0.762920076479267</v>
       </c>
       <c r="P10" t="n">
         <v>0.2191554354725503</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1224736626770367</v>
+        <v>0.06457639515807267</v>
       </c>
       <c r="R10" t="n">
-        <v>0.07424617312978121</v>
+        <v>0.000752762724490097</v>
       </c>
       <c r="S10" t="n">
         <v>0.1050612845834679</v>
@@ -1338,6 +1367,9 @@
       </c>
       <c r="Z10" t="n">
         <v>0.338712995102226</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>434</v>
       </c>
     </row>
     <row r="11">
@@ -1380,28 +1412,28 @@
         <v>-0.02690173803271029</v>
       </c>
       <c r="K11" t="n">
-        <v>0.09013509971849361</v>
+        <v>0.1034789583949496</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7654931805333591</v>
+        <v>0.7950064619995394</v>
       </c>
       <c r="M11" t="n">
         <v>0.004373922794425056</v>
       </c>
       <c r="N11" t="n">
-        <v>0.08580179042821556</v>
+        <v>0.04009793090170225</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9593669884911344</v>
+        <v>0.913188078679128</v>
       </c>
       <c r="P11" t="n">
         <v>0.1961867092588476</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1137628302368161</v>
+        <v>0.05429929062812547</v>
       </c>
       <c r="R11" t="n">
-        <v>0.08531722025896693</v>
+        <v>0.0003376086462281158</v>
       </c>
       <c r="S11" t="n">
         <v>0.2072718554409908</v>
@@ -1426,6 +1458,9 @@
       </c>
       <c r="Z11" t="n">
         <v>0.3151825228869206</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>439</v>
       </c>
     </row>
     <row r="12">
@@ -1468,28 +1503,28 @@
         <v>-0.04929591654731119</v>
       </c>
       <c r="K12" t="n">
-        <v>0.08849858097863554</v>
+        <v>0.1048019561847528</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5777929716238019</v>
+        <v>0.6383217300721258</v>
       </c>
       <c r="M12" t="n">
         <v>-0.004339375074473406</v>
       </c>
       <c r="N12" t="n">
-        <v>0.08156096999198173</v>
+        <v>0.03338814201054206</v>
       </c>
       <c r="O12" t="n">
-        <v>0.9575934096785721</v>
+        <v>0.8966513583870233</v>
       </c>
       <c r="P12" t="n">
         <v>0.1727825374767906</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1093528399551743</v>
+        <v>0.0565645001763239</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1148132353638542</v>
+        <v>0.00239011215106677</v>
       </c>
       <c r="S12" t="n">
         <v>0.3659100716749622</v>
@@ -1514,6 +1549,9 @@
       </c>
       <c r="Z12" t="n">
         <v>0.3006611222339646</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>441</v>
       </c>
     </row>
     <row r="13">
@@ -1556,28 +1594,28 @@
         <v>-0.005893311295613213</v>
       </c>
       <c r="K13" t="n">
-        <v>0.08493846454147885</v>
+        <v>0.1054875546959835</v>
       </c>
       <c r="L13" t="n">
-        <v>0.9447158967789728</v>
+        <v>0.9554727169603434</v>
       </c>
       <c r="M13" t="n">
         <v>-0.002937585010328717</v>
       </c>
       <c r="N13" t="n">
-        <v>0.07896591941327742</v>
+        <v>0.03364615891929734</v>
       </c>
       <c r="O13" t="n">
-        <v>0.9703418006067994</v>
+        <v>0.9304660890695318</v>
       </c>
       <c r="P13" t="n">
         <v>0.2008770177785392</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.1091958704520013</v>
+        <v>0.05243650790642856</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0664970263123521</v>
+        <v>0.0001461745198700903</v>
       </c>
       <c r="S13" t="n">
         <v>0.04761166818817734</v>
@@ -1602,6 +1640,9 @@
       </c>
       <c r="Z13" t="n">
         <v>0.2350710624732134</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>442</v>
       </c>
     </row>
     <row r="14">
@@ -1644,28 +1685,28 @@
         <v>0.005018566042800515</v>
       </c>
       <c r="K14" t="n">
-        <v>0.08740571315205253</v>
+        <v>0.1046617467270387</v>
       </c>
       <c r="L14" t="n">
-        <v>0.95423909813853</v>
+        <v>0.9617775296413034</v>
       </c>
       <c r="M14" t="n">
         <v>0.01224683582631203</v>
       </c>
       <c r="N14" t="n">
-        <v>0.08348352438797091</v>
+        <v>0.04459928300890901</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8834377199505665</v>
+        <v>0.783754348508078</v>
       </c>
       <c r="P14" t="n">
         <v>0.2208294892241674</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1153684564797534</v>
+        <v>0.05053420143582366</v>
       </c>
       <c r="R14" t="n">
-        <v>0.05625126398205471</v>
+        <v>1.551603234850596e-05</v>
       </c>
       <c r="S14" t="n">
         <v>0.04251157654039526</v>
@@ -1690,6 +1731,9 @@
       </c>
       <c r="Z14" t="n">
         <v>0.2442144654768807</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>441</v>
       </c>
     </row>
     <row r="15">
@@ -1732,28 +1776,28 @@
         <v>-0.01789116889871011</v>
       </c>
       <c r="K15" t="n">
-        <v>0.08549286737388682</v>
+        <v>0.1067313695003041</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8343336240342616</v>
+        <v>0.8669529367828428</v>
       </c>
       <c r="M15" t="n">
         <v>0.01761429226320586</v>
       </c>
       <c r="N15" t="n">
-        <v>0.07297182576773384</v>
+        <v>0.03222459795372994</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8093693115093483</v>
+        <v>0.5849236734881864</v>
       </c>
       <c r="P15" t="n">
         <v>0.2098153262066337</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1062895425475514</v>
+        <v>0.05481374522790179</v>
       </c>
       <c r="R15" t="n">
-        <v>0.04900706124524468</v>
+        <v>0.0001480413992962504</v>
       </c>
       <c r="S15" t="n">
         <v>0.1577752340275287</v>
@@ -1778,6 +1822,9 @@
       </c>
       <c r="Z15" t="n">
         <v>0.2536644278165219</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>440</v>
       </c>
     </row>
     <row r="16">
@@ -1820,28 +1867,28 @@
         <v>0.006841298475382257</v>
       </c>
       <c r="K16" t="n">
-        <v>0.08455664794244065</v>
+        <v>0.1021113197160294</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9355519238850687</v>
+        <v>0.9466133137518176</v>
       </c>
       <c r="M16" t="n">
         <v>-0.006341097771190879</v>
       </c>
       <c r="N16" t="n">
-        <v>0.08046583670173586</v>
+        <v>0.0317910227353181</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9372235950727648</v>
+        <v>0.8419933790990031</v>
       </c>
       <c r="P16" t="n">
         <v>0.2083804599905848</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.1091818717004458</v>
+        <v>0.04690714992574883</v>
       </c>
       <c r="R16" t="n">
-        <v>0.05696744252827446</v>
+        <v>1.126274850449249e-05</v>
       </c>
       <c r="S16" t="n">
         <v>0.05460636679013595</v>
@@ -1866,6 +1913,9 @@
       </c>
       <c r="Z16" t="n">
         <v>0.2400270433502746</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>441</v>
       </c>
     </row>
     <row r="17">
@@ -1908,28 +1958,28 @@
         <v>-0.004587870131853924</v>
       </c>
       <c r="K17" t="n">
-        <v>0.08634306907404116</v>
+        <v>0.1068227876149894</v>
       </c>
       <c r="L17" t="n">
-        <v>0.9576480097092415</v>
+        <v>0.9657620002458995</v>
       </c>
       <c r="M17" t="n">
         <v>-0.003998859353855813</v>
       </c>
       <c r="N17" t="n">
-        <v>0.07860247978150307</v>
+        <v>0.03188092648263212</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9594484811325019</v>
+        <v>0.9002391774103418</v>
       </c>
       <c r="P17" t="n">
         <v>0.2011443941575537</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.110051512784309</v>
+        <v>0.05217882393548783</v>
       </c>
       <c r="R17" t="n">
-        <v>0.06826262145077289</v>
+        <v>0.0001329114897625772</v>
       </c>
       <c r="S17" t="n">
         <v>0.03673790886869514</v>
@@ -1954,6 +2004,9 @@
       </c>
       <c r="Z17" t="n">
         <v>0.2344793471696709</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>443</v>
       </c>
     </row>
     <row r="18">
@@ -1996,28 +2049,28 @@
         <v>-0.1641684174738484</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0945446491607419</v>
+        <v>0.1006011755786994</v>
       </c>
       <c r="L18" t="n">
-        <v>0.08320070799597001</v>
+        <v>0.1034314271898242</v>
       </c>
       <c r="M18" t="n">
         <v>-0.03377957919252025</v>
       </c>
       <c r="N18" t="n">
-        <v>0.03869652304656652</v>
+        <v>0.02634325998463249</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3831807977694486</v>
+        <v>0.2004270182270753</v>
       </c>
       <c r="P18" t="n">
         <v>0.05707942162693071</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.1075090585158286</v>
+        <v>0.09641569988019343</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5957412100207171</v>
+        <v>0.554149642614157</v>
       </c>
       <c r="S18" t="n">
         <v>1.633944816256412</v>
@@ -2042,6 +2095,9 @@
       </c>
       <c r="Z18" t="n">
         <v>0.3496407568283366</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>434</v>
       </c>
     </row>
     <row r="19">
@@ -2084,28 +2140,28 @@
         <v>-0.1916220243525119</v>
       </c>
       <c r="K19" t="n">
-        <v>0.08605113305655729</v>
+        <v>0.09392648760619908</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0264645680275668</v>
+        <v>0.04193557339511789</v>
       </c>
       <c r="M19" t="n">
         <v>-0.01656351923638708</v>
       </c>
       <c r="N19" t="n">
-        <v>0.04162170040601392</v>
+        <v>0.02711838419010966</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6908575939252999</v>
+        <v>0.5416576035381162</v>
       </c>
       <c r="P19" t="n">
         <v>0.04707035502939569</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.10145161271346</v>
+        <v>0.09245120807138521</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6429002728063056</v>
+        <v>0.6109118190597251</v>
       </c>
       <c r="S19" t="n">
         <v>1.938980608376613</v>
@@ -2130,6 +2186,9 @@
       </c>
       <c r="Z19" t="n">
         <v>0.333733725899572</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>439</v>
       </c>
     </row>
     <row r="20">
@@ -2172,28 +2231,28 @@
         <v>-0.2129134325110132</v>
       </c>
       <c r="K20" t="n">
-        <v>0.09127175985279461</v>
+        <v>0.1029893825810148</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02011067903613784</v>
+        <v>0.03928555842570658</v>
       </c>
       <c r="M20" t="n">
         <v>-0.02340417174706023</v>
       </c>
       <c r="N20" t="n">
-        <v>0.03956810630090955</v>
+        <v>0.02710289849606878</v>
       </c>
       <c r="O20" t="n">
-        <v>0.554494670691613</v>
+        <v>0.3883154121287493</v>
       </c>
       <c r="P20" t="n">
         <v>0.02200665710681832</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.1041941853568474</v>
+        <v>0.09891339488129695</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8328224459999687</v>
+        <v>0.8240400557355017</v>
       </c>
       <c r="S20" t="n">
         <v>2.095011067261121</v>
@@ -2218,6 +2277,9 @@
       </c>
       <c r="Z20" t="n">
         <v>0.3247912492412734</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>441</v>
       </c>
     </row>
     <row r="21">
@@ -2260,28 +2322,28 @@
         <v>-0.1743801508006306</v>
       </c>
       <c r="K21" t="n">
-        <v>0.09744282500950603</v>
+        <v>0.1090001877049711</v>
       </c>
       <c r="L21" t="n">
-        <v>0.07420855582883124</v>
+        <v>0.1103541041653806</v>
       </c>
       <c r="M21" t="n">
         <v>-0.02924392372755673</v>
       </c>
       <c r="N21" t="n">
-        <v>0.03586224386718907</v>
+        <v>0.02207651359051792</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4152530579993172</v>
+        <v>0.1859676728786726</v>
       </c>
       <c r="P21" t="n">
         <v>0.04151513068744797</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.1126330060683895</v>
+        <v>0.09348197398977626</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7126116062366326</v>
+        <v>0.6571892812396358</v>
       </c>
       <c r="S21" t="n">
         <v>1.773648720439685</v>
@@ -2306,6 +2368,9 @@
       </c>
       <c r="Z21" t="n">
         <v>0.2543232147727231</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>442</v>
       </c>
     </row>
     <row r="22">
@@ -2348,28 +2413,28 @@
         <v>-0.1614790012008076</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1028991652887455</v>
+        <v>0.107202352486816</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1172967422619837</v>
+        <v>0.1327058782740489</v>
       </c>
       <c r="M22" t="n">
         <v>-0.01806578947358668</v>
       </c>
       <c r="N22" t="n">
-        <v>0.03986827281565793</v>
+        <v>0.0276805371507727</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6506729611863624</v>
+        <v>0.5143199803109129</v>
       </c>
       <c r="P22" t="n">
         <v>0.06378473149136982</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.1195917433830061</v>
+        <v>0.09016968593059155</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5940572621155364</v>
+        <v>0.4797005655590068</v>
       </c>
       <c r="S22" t="n">
         <v>1.711349115486978</v>
@@ -2394,6 +2459,9 @@
       </c>
       <c r="Z22" t="n">
         <v>0.2598293416297719</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>441</v>
       </c>
     </row>
     <row r="23">
@@ -2436,28 +2504,28 @@
         <v>-0.1925059826812914</v>
       </c>
       <c r="K23" t="n">
-        <v>0.09015771029380448</v>
+        <v>0.1008901858869583</v>
       </c>
       <c r="L23" t="n">
-        <v>0.03329525236678332</v>
+        <v>0.05703218090655149</v>
       </c>
       <c r="M23" t="n">
         <v>-0.005864671243464667</v>
       </c>
       <c r="N23" t="n">
-        <v>0.03221052971686993</v>
+        <v>0.02365791287688258</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8556092046209027</v>
+        <v>0.8043315233397057</v>
       </c>
       <c r="P23" t="n">
         <v>0.05338367877332142</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.1047855352793396</v>
+        <v>0.09749817606424976</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6106876449304313</v>
+        <v>0.5842887488671988</v>
       </c>
       <c r="S23" t="n">
         <v>2.264254298168175</v>
@@ -2482,6 +2550,9 @@
       </c>
       <c r="Z23" t="n">
         <v>0.2783776763754089</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>440</v>
       </c>
     </row>
     <row r="24">
@@ -2524,28 +2595,28 @@
         <v>-0.1669002789839438</v>
       </c>
       <c r="K24" t="n">
-        <v>0.09591289885673115</v>
+        <v>0.1056582138786054</v>
       </c>
       <c r="L24" t="n">
-        <v>0.08253493398956468</v>
+        <v>0.1149098953447429</v>
       </c>
       <c r="M24" t="n">
         <v>-0.03559012186479286</v>
       </c>
       <c r="N24" t="n">
-        <v>0.03804302824873673</v>
+        <v>0.02037012322265147</v>
       </c>
       <c r="O24" t="n">
-        <v>0.3500309076714447</v>
+        <v>0.08130348351005035</v>
       </c>
       <c r="P24" t="n">
         <v>0.04148209201771125</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.110412427849922</v>
+        <v>0.08556976725601137</v>
       </c>
       <c r="R24" t="n">
-        <v>0.7073196260039656</v>
+        <v>0.6280765875654173</v>
       </c>
       <c r="S24" t="n">
         <v>1.628447366728014</v>
@@ -2570,6 +2641,9 @@
       </c>
       <c r="Z24" t="n">
         <v>0.2566272114239887</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>441</v>
       </c>
     </row>
     <row r="25">
@@ -2612,28 +2686,28 @@
         <v>-0.1688389564772287</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1023281812440728</v>
+        <v>0.1119575746091524</v>
       </c>
       <c r="L25" t="n">
-        <v>0.09965682033661971</v>
+        <v>0.1322514787127145</v>
       </c>
       <c r="M25" t="n">
         <v>-0.033299153512956</v>
       </c>
       <c r="N25" t="n">
-        <v>0.03602259573994106</v>
+        <v>0.01981659899165199</v>
       </c>
       <c r="O25" t="n">
-        <v>0.3557832732970749</v>
+        <v>0.09359092919670275</v>
       </c>
       <c r="P25" t="n">
         <v>0.04302945693132915</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.1161637041057611</v>
+        <v>0.09295404268679792</v>
       </c>
       <c r="R25" t="n">
-        <v>0.7112459916471487</v>
+        <v>0.643655409045695</v>
       </c>
       <c r="S25" t="n">
         <v>1.666368625137859</v>
@@ -2658,6 +2732,9 @@
       </c>
       <c r="Z25" t="n">
         <v>0.2523589750532466</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>443</v>
       </c>
     </row>
   </sheetData>
